--- a/AircraftTypeEngineFuelFlowData.xlsx
+++ b/AircraftTypeEngineFuelFlowData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ianct\source\repos\ProductionProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA7DBD7-A631-4267-925E-7427B1F30006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81978BF2-4F87-4AF2-8C88-C03AA61925A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{A01ED7BC-7C36-4491-9F5D-3651E3725D85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>Fuel Flow T/O (kg/sec)</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>PW PW4056</t>
+  </si>
+  <si>
+    <t>Fuel Flow Idle (kg/sec)</t>
+  </si>
+  <si>
+    <t>10% of cruise level</t>
   </si>
 </sst>
 </file>
@@ -203,7 +209,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -246,6 +252,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -283,7 +295,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -314,7 +326,16 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -661,17 +682,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B678DB-D012-4F40-A47F-28BF32F8ABBA}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" customWidth="1"/>
     <col min="6" max="6" width="16.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="27.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -693,11 +715,14 @@
       <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -720,10 +745,13 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="H2" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0.113</v>
+      </c>
+      <c r="I2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -742,11 +770,14 @@
       <c r="G3" s="7">
         <v>0.316</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H3" s="7">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>11</v>
       </c>
@@ -762,11 +793,14 @@
       <c r="G4" s="9">
         <v>0.3901</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H4" s="9">
+        <v>0.1363</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>15</v>
       </c>
@@ -782,11 +816,14 @@
       <c r="G5" s="9">
         <v>0.32600000000000001</v>
       </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H5" s="9">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>18</v>
       </c>
@@ -802,11 +839,14 @@
       <c r="G6" s="3">
         <v>0.63200000000000001</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="3">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>20</v>
       </c>
@@ -825,11 +865,14 @@
       <c r="G7" s="9">
         <v>0.23219400000000001</v>
       </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H7" s="9">
+        <v>8.9743000000000003E-2</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>21</v>
       </c>
@@ -845,11 +888,14 @@
       <c r="G8" s="9">
         <v>0.27834199999999998</v>
       </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H8" s="14">
+        <v>9.8799999999999999E-2</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>22</v>
       </c>
@@ -865,11 +911,14 @@
       <c r="G9" s="3">
         <v>0.33800000000000002</v>
       </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H9" s="3">
+        <v>0.113</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>23</v>
       </c>
@@ -885,11 +934,14 @@
       <c r="G10" s="11">
         <v>0.84</v>
       </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H10" s="11">
+        <v>0.27</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>24</v>
       </c>
@@ -905,11 +957,14 @@
       <c r="G11" s="11">
         <v>0.84</v>
       </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11" s="11">
+        <v>0.27</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>25</v>
       </c>
@@ -925,30 +980,45 @@
       <c r="G12" s="7">
         <v>1.1299999999999999</v>
       </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H12" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E13" s="8">
+        <v>2.7090000000000001</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2.202</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>29</v>
       </c>
@@ -964,11 +1034,14 @@
       <c r="G15" s="8">
         <v>0.221</v>
       </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H15" s="8">
+        <v>0.113</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>31</v>
       </c>
@@ -985,15 +1058,18 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="H16" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.113</v>
+      </c>
+      <c r="I16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>40</v>
       </c>
@@ -1009,11 +1085,14 @@
       <c r="G18" s="10">
         <v>1.39547948434724</v>
       </c>
-      <c r="H18" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H18" s="15">
+        <v>0.113</v>
+      </c>
+      <c r="I18" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>28</v>
       </c>
@@ -1030,12 +1109,23 @@
         <v>0.64700000000000002</v>
       </c>
       <c r="H19" s="1">
+        <v>0.1981</v>
+      </c>
+      <c r="I19" s="1">
         <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="E1:H1">
+  <conditionalFormatting sqref="E1:I1">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>" "</formula>
     </cfRule>
